--- a/agent_workflows/vibe_coding/config/pairing_review_workbook.xlsx
+++ b/agent_workflows/vibe_coding/config/pairing_review_workbook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pnnl-my.sharepoint.com/personal/jake_cavaiani_pnnl_gov/Documents/Documents/GitHub/rc_sfa-rc-3-wenas-meta/agent_workflows/vibe_coding/config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/allisonmyerspigg/GitHub/rc_sfa-rc-3-wenas-meta/agent_workflows/vibe_coding/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="283" documentId="13_ncr:1_{77E1BE90-A583-204A-ADB5-A1FAB842CF85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FDBD09F7-D57C-3A4D-B3B6-3D5B392B21BB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD26EAE-A6BB-654D-B03A-725FFC7C636B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-10960" yWindow="-31240" windowWidth="68740" windowHeight="18780" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15060" yWindow="-31240" windowWidth="64240" windowHeight="24460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="346">
   <si>
     <t>Watershed Pairing Review</t>
   </si>
@@ -958,16 +958,7 @@
     <t xml:space="preserve">Figure 1 in the paper shows a map of the burn perimeter and the sampling locations. There are 3 burned watersheds (Site 2, Site 3, and Site 4) that are all associated with the Angora Fire. All 3 of these sites are compared to 1 reference site (Site 1). </t>
   </si>
   <si>
-    <t xml:space="preserve">This study investigates 3 burned sites along Angora Creek that are associated with the Angora Fire. Site 1 was selected to represent the initial conditions of Angora Creek. Site 2 was within the burn area, Site 3 was located just below the burned area and site 4 was located downstream of the burn. We need to decide if they are "different" sites since they are all on the same creek. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Figure 1 in the paper shows a map of the burn perimeter and the sampling locations. There are 2 burned watersheds (PNF, PSF) that are both associated with the High Park Fire. Both of these sites are compared to 1 reference site (PBR). </t>
-  </si>
-  <si>
-    <t xml:space="preserve">This study investigates 2 burned watersheds associated with the High Park Fire. Both burned watersheds (PNF, and PSF) compare to a single reference site (PBR). These are the same sites as from Writer et al. I think because Writer has both DOC and NO3 compared to this one that is just DOC, we should keep Writer and remove the redudancy of this paper.   </t>
-  </si>
-  <si>
-    <t>This study investigates 4 burned watersheds associated with the Pole Creek Fire Complex and 6 unburned watersheds. The burn unburned pairs can get a little convuluted and we need to discuss what is best. The paper aggregated burned vs. unburned in the rest of the statistical analyses (Fig 3-8). Mulitple reference sites to 1 burn.</t>
   </si>
   <si>
     <t xml:space="preserve">Scotty Creek (SC) and Notawohka Creek (NW) drain catchments located in the discontinuous permafrost zone of Canada’s western boreal forest (Fig. 1). The SC outlet at the Liard Highway (61◦24 W, 121◦26 N) has a 134 km2 catchment that has not been affected by any major fires in the last 60 years. The NW outlet at the Mackenzie Highway (61◦08 W, 120◦17 N) has a 321 km2 catchment that was &gt;90 % burned in 2013. FIgure 4: Seasonal variation in catchment run-off and stream water chemistry measured at the outlets of Scotty Creek catchment and the
@@ -1050,6 +1041,34 @@
   </si>
   <si>
     <t>There are multiple burned watersheds to a single reference site. This paper has 2 fires (High Park and Hayman Fire). B2 and B3 go to U3 (Hayman Fire). B1 go to U1 and U2 (High Park). U3 is designated as Control_2_3 because it is used to compare between Site 2 (B2) and Site 3 (B3)</t>
+  </si>
+  <si>
+    <t>This paper investigates 2 burned sampling locations (PSF, PNF) and compares to the same reference site (PBR). 
+Yes, relate to high park fire (AMP)</t>
+  </si>
+  <si>
+    <t>This study investigates 3 burned sites along Angora Creek that are associated with the Angora Fire. Site 1 was selected to represent the initial conditions of Angora Creek. Site 2 was within the burn area, Site 3 was located just below the burned area and site 4 was located downstream of the burn. We need to decide if they are "different" sites since they are all on the same creek. 
+Pick the most downstream site and remove the others. (AMP)</t>
+  </si>
+  <si>
+    <t>This study investigates 3 burned sites along Angora Creek that are associated with the Angora Fire. Site 1 was selected to represent the initial conditions of Angora Creek. Site 2 was within the burn area, Site 3 was located just below the burned area and site 4 was located downstream of the burn. We need to decide if they are "different" sites since they are all on the same creek. 
+Pick the most downstream site and remove the others. (AMP)</t>
+  </si>
+  <si>
+    <t>This study investigates 2 burned watersheds associated with the High Park Fire. Both burned watersheds (PNF, and PSF) compare to a single reference site (PBR). These are the same sites as from Writer et al. I think because Writer has both DOC and NO3 compared to this one that is just DOC, we should keep Writer and remove the redudancy of this paper.   
+I think this paper has higher temporal resolution than Writer? (AMP) If not, do they over lap in time? If so, then ok to drop. if not, retain (AMP)</t>
+  </si>
+  <si>
+    <t>This study investigates 4 burned watersheds associated with the Pole Creek Fire Complex and 6 unburned watersheds. The burn unburned pairs can get a little convuluted and we need to discuss what is best. The paper aggregated burned vs. unburned in the rest of the statistical analyses (Fig 3-8). Mulitple reference sites to 1 burn.
+I am OK with retaining the burned and unburned comparisions stated in the Figure 1 Evidence source. (AMP)</t>
+  </si>
+  <si>
+    <t>This study investigates 4 burned watersheds associated with the Pole Creek Fire Complex and 6 unburned watersheds. The burn unburned pairs can get a little convuluted and we need to discuss what is best. The paper aggregated burned vs. unburned in the rest of the statistical analyses (Fig 3-8). Mulitple reference sites to 1 burn.
+I am OK with retaining the burned and unburned comparisions stated in the Figure 1 Evidence source. Why is the Spanish Fork not showing up as a line on this study?? (AMP)</t>
+  </si>
+  <si>
+    <t>There are multiple burned watersheds to a single reference site. This paper has 2 fires (High Park and Hayman Fire). B2 and B3 go to U3 (Hayman Fire). B1 go to U1 and U2 (High Park).
+I am confused about their study design too. This is also missing the Hayman fire comparisons as a line in paring worksheet here. Looking at table 1, can you pick the one reference thats closest in size to the burn here? e.g. U1 is smaller than U2, so use that to comapre to B1. For B2 and B3, they share the same reference so easier to denote the burned / unburned pair. (AMP)</t>
   </si>
 </sst>
 </file>
@@ -1174,7 +1193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1184,9 +1203,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1211,7 +1227,9 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1594,10 +1612,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="26" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
+      <c r="B1" s="13"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
@@ -1792,195 +1810,195 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:32" s="6" customFormat="1" ht="80" x14ac:dyDescent="0.2">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:32" s="5" customFormat="1" ht="80" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="10" t="s">
+      <c r="D2" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="10" t="s">
+      <c r="F2" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="G2" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I2" s="10" t="s">
+      <c r="I2" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="J2" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="K2" s="10" t="s">
+      <c r="K2" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="L2" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="M2" s="10">
+      <c r="M2" s="9">
         <v>2017</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="9">
         <v>2017</v>
       </c>
-      <c r="O2" s="10">
-        <v>1</v>
-      </c>
-      <c r="P2" s="10" t="s">
+      <c r="O2" s="9">
+        <v>1</v>
+      </c>
+      <c r="P2" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="9">
         <v>2</v>
       </c>
-      <c r="R2" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="S2" s="10" t="b">
-        <v>1</v>
-      </c>
-      <c r="T2" s="10" t="s">
+      <c r="R2" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="S2" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="U2" s="10" t="s">
+      <c r="U2" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="V2" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="W2" s="7" t="s">
+      <c r="V2" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="W2" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X2" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="7" t="s">
+      <c r="X2" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z2" s="7" t="s">
+      <c r="Z2" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="AA2" s="7" t="s">
+      <c r="AA2" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB2" s="8">
+      <c r="AB2" s="7">
         <v>46265</v>
       </c>
-      <c r="AC2" s="7" t="s">
-        <v>341</v>
-      </c>
-      <c r="AD2" s="12"/>
-      <c r="AE2" s="14"/>
-      <c r="AF2" s="14"/>
-    </row>
-    <row r="3" spans="1:32" s="6" customFormat="1" ht="80" x14ac:dyDescent="0.2">
-      <c r="A3" s="5" t="s">
+      <c r="AC2" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="AD2" s="11"/>
+      <c r="AE2"/>
+      <c r="AF2"/>
+    </row>
+    <row r="3" spans="1:32" s="5" customFormat="1" ht="80" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="I3" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="L3" s="11" t="s">
+      <c r="L3" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="M3" s="11">
+      <c r="M3" s="10">
         <v>2017</v>
       </c>
-      <c r="N3" s="11">
+      <c r="N3" s="10">
         <v>2017</v>
       </c>
-      <c r="O3" s="11">
-        <v>1</v>
-      </c>
-      <c r="P3" s="11" t="s">
+      <c r="O3" s="10">
+        <v>1</v>
+      </c>
+      <c r="P3" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="Q3" s="11">
+      <c r="Q3" s="10">
         <v>2</v>
       </c>
-      <c r="R3" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="S3" s="11" t="b">
-        <v>1</v>
-      </c>
-      <c r="T3" s="11" t="s">
+      <c r="R3" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="S3" s="10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="U3" s="11" t="s">
+      <c r="U3" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="V3" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="W3" s="7" t="s">
+      <c r="V3" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="W3" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X3" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="7" t="s">
+      <c r="X3" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z3" s="7" t="s">
+      <c r="Z3" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="AA3" s="7" t="s">
+      <c r="AA3" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB3" s="8">
+      <c r="AB3" s="7">
         <v>46265</v>
       </c>
-      <c r="AC3" s="7" t="s">
+      <c r="AC3" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="AD3" s="12"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
+      <c r="AD3" s="11"/>
+      <c r="AE3"/>
+      <c r="AF3"/>
     </row>
     <row r="4" spans="1:32" ht="112" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="1" t="s">
@@ -2040,28 +2058,28 @@
       <c r="U4" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V4" s="7" t="s">
-        <v>324</v>
-      </c>
-      <c r="W4" s="7" t="s">
+      <c r="V4" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="W4" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X4" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="7" t="s">
+      <c r="X4" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z4" s="7" t="s">
+      <c r="Z4" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="AA4" s="7" t="s">
+      <c r="AA4" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB4" s="8">
+      <c r="AB4" s="7">
         <v>46265</v>
       </c>
-      <c r="AC4" s="7" t="s">
+      <c r="AC4" s="6" t="s">
         <v>290</v>
       </c>
     </row>
@@ -2129,28 +2147,28 @@
       <c r="U5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V5" s="7" t="s">
-        <v>325</v>
-      </c>
-      <c r="W5" s="7" t="s">
+      <c r="V5" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="W5" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X5" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="7" t="s">
+      <c r="X5" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z5" s="7" t="s">
+      <c r="Z5" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="AA5" s="7" t="s">
+      <c r="AA5" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB5" s="8">
+      <c r="AB5" s="7">
         <v>46265</v>
       </c>
-      <c r="AC5" s="7" t="s">
+      <c r="AC5" s="6" t="s">
         <v>290</v>
       </c>
     </row>
@@ -2218,29 +2236,29 @@
       <c r="U6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V6" s="7" t="s">
-        <v>326</v>
-      </c>
-      <c r="W6" s="7" t="s">
+      <c r="V6" s="6" t="s">
+        <v>323</v>
+      </c>
+      <c r="W6" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X6" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="Z6" s="7" t="s">
+      <c r="X6" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z6" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="AA6" s="7" t="s">
+      <c r="AA6" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB6" s="8">
+      <c r="AB6" s="7">
         <v>46265</v>
       </c>
-      <c r="AC6" s="7" t="s">
-        <v>292</v>
+      <c r="AC6" s="6" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="256" x14ac:dyDescent="0.2">
@@ -2307,28 +2325,28 @@
       <c r="U7" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V7" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="W7" s="7" t="s">
+      <c r="V7" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="W7" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X7" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="Z7" s="7" t="s">
+      <c r="X7" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z7" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="AA7" s="7" t="s">
+      <c r="AA7" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB7" s="8">
+      <c r="AB7" s="7">
         <v>46265</v>
       </c>
-      <c r="AC7" s="7" t="s">
+      <c r="AC7" s="6" t="s">
         <v>292</v>
       </c>
     </row>
@@ -2396,28 +2414,28 @@
       <c r="U8" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="V8" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="W8" s="7" t="s">
+      <c r="V8" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="W8" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="X8" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="7" t="s">
+      <c r="X8" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z8" s="7" t="s">
+      <c r="Z8" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="AA8" s="7" t="s">
+      <c r="AA8" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB8" s="8">
+      <c r="AB8" s="7">
         <v>46265</v>
       </c>
-      <c r="AC8" s="7" t="s">
+      <c r="AC8" s="6" t="s">
         <v>294</v>
       </c>
     </row>
@@ -2485,28 +2503,28 @@
       <c r="U9" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="V9" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="W9" s="7" t="s">
+      <c r="V9" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="W9" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="X9" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="7" t="s">
+      <c r="X9" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z9" s="7" t="s">
+      <c r="Z9" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="AA9" s="7" t="s">
+      <c r="AA9" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB9" s="8">
+      <c r="AB9" s="7">
         <v>46265</v>
       </c>
-      <c r="AC9" s="7" t="s">
+      <c r="AC9" s="6" t="s">
         <v>294</v>
       </c>
     </row>
@@ -2574,28 +2592,28 @@
       <c r="U10" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="V10" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="W10" s="7" t="s">
+      <c r="V10" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="W10" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="X10" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="7" t="s">
+      <c r="X10" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z10" s="7" t="s">
+      <c r="Z10" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="AA10" s="7" t="s">
+      <c r="AA10" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB10" s="8">
+      <c r="AB10" s="7">
         <v>46265</v>
       </c>
-      <c r="AC10" s="7" t="s">
+      <c r="AC10" s="6" t="s">
         <v>296</v>
       </c>
     </row>
@@ -2663,29 +2681,29 @@
       <c r="U11" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="V11" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="W11" s="7" t="s">
+      <c r="V11" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="W11" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="X11" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="Z11" s="7" t="s">
+      <c r="X11" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z11" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="AA11" s="7" t="s">
+      <c r="AA11" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB11" s="8">
+      <c r="AB11" s="7">
         <v>46265</v>
       </c>
-      <c r="AC11" s="7" t="s">
-        <v>297</v>
+      <c r="AC11" s="6" t="s">
+        <v>345</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="80" x14ac:dyDescent="0.2">
@@ -2752,28 +2770,28 @@
       <c r="U12" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V12" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="W12" s="7" t="s">
+      <c r="V12" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="W12" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X12" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="7" t="s">
+      <c r="X12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z12" s="7" t="s">
+      <c r="Z12" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="AA12" s="7" t="s">
+      <c r="AA12" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB12" s="8">
+      <c r="AB12" s="7">
         <v>46265</v>
       </c>
-      <c r="AC12" s="7" t="s">
+      <c r="AC12" s="6" t="s">
         <v>301</v>
       </c>
     </row>
@@ -2841,28 +2859,28 @@
       <c r="U13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V13" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="W13" s="7" t="s">
+      <c r="V13" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="W13" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X13" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="7" t="s">
+      <c r="X13" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z13" s="7" t="s">
+      <c r="Z13" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="AA13" s="7" t="s">
+      <c r="AA13" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB13" s="8">
+      <c r="AB13" s="7">
         <v>46265</v>
       </c>
-      <c r="AC13" s="7" t="s">
+      <c r="AC13" s="6" t="s">
         <v>301</v>
       </c>
     </row>
@@ -2930,28 +2948,28 @@
       <c r="U14" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V14" s="7" t="s">
-        <v>331</v>
-      </c>
-      <c r="W14" s="7" t="s">
+      <c r="V14" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="W14" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X14" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="7" t="s">
+      <c r="X14" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z14" s="7" t="s">
+      <c r="Z14" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="AA14" s="7" t="s">
+      <c r="AA14" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB14" s="8">
+      <c r="AB14" s="7">
         <v>46265</v>
       </c>
-      <c r="AC14" s="7" t="s">
+      <c r="AC14" s="6" t="s">
         <v>301</v>
       </c>
     </row>
@@ -3019,28 +3037,28 @@
       <c r="U15" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V15" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="W15" s="7" t="s">
+      <c r="V15" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="W15" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X15" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="7" t="s">
+      <c r="X15" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z15" s="7" t="s">
+      <c r="Z15" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="AA15" s="7" t="s">
+      <c r="AA15" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB15" s="8">
+      <c r="AB15" s="7">
         <v>46265</v>
       </c>
-      <c r="AC15" s="7" t="s">
+      <c r="AC15" s="6" t="s">
         <v>303</v>
       </c>
     </row>
@@ -3108,28 +3126,28 @@
       <c r="U16" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V16" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="W16" s="7" t="s">
+      <c r="V16" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="W16" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X16" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="7" t="s">
+      <c r="X16" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z16" s="7" t="s">
+      <c r="Z16" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="AA16" s="7" t="s">
+      <c r="AA16" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB16" s="8">
+      <c r="AB16" s="7">
         <v>46265</v>
       </c>
-      <c r="AC16" s="7" t="s">
+      <c r="AC16" s="6" t="s">
         <v>303</v>
       </c>
     </row>
@@ -3197,28 +3215,28 @@
       <c r="U17" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V17" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="W17" s="7" t="s">
+      <c r="V17" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="W17" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X17" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="7" t="s">
+      <c r="X17" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z17" s="7" t="s">
+      <c r="Z17" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="AA17" s="7" t="s">
+      <c r="AA17" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB17" s="8">
+      <c r="AB17" s="7">
         <v>46265</v>
       </c>
-      <c r="AC17" s="7" t="s">
+      <c r="AC17" s="6" t="s">
         <v>305</v>
       </c>
     </row>
@@ -3286,28 +3304,28 @@
       <c r="U18" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V18" s="7" t="s">
-        <v>333</v>
-      </c>
-      <c r="W18" s="7" t="s">
+      <c r="V18" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="W18" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X18" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y18" s="7" t="s">
+      <c r="X18" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z18" s="7" t="s">
+      <c r="Z18" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="AA18" s="7" t="s">
+      <c r="AA18" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB18" s="8">
+      <c r="AB18" s="7">
         <v>46265</v>
       </c>
-      <c r="AC18" s="7" t="s">
+      <c r="AC18" s="6" t="s">
         <v>305</v>
       </c>
     </row>
@@ -3375,28 +3393,28 @@
       <c r="U19" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V19" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="W19" s="7" t="s">
+      <c r="V19" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="W19" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X19" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="7" t="s">
+      <c r="X19" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z19" s="7" t="s">
+      <c r="Z19" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="AA19" s="7" t="s">
+      <c r="AA19" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB19" s="8">
+      <c r="AB19" s="7">
         <v>46265</v>
       </c>
-      <c r="AC19" s="7" t="s">
+      <c r="AC19" s="6" t="s">
         <v>307</v>
       </c>
     </row>
@@ -3464,28 +3482,28 @@
       <c r="U20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V20" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="W20" s="7" t="s">
+      <c r="V20" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="W20" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X20" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y20" s="7" t="s">
+      <c r="X20" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z20" s="7" t="s">
+      <c r="Z20" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="AA20" s="7" t="s">
+      <c r="AA20" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB20" s="8">
+      <c r="AB20" s="7">
         <v>46265</v>
       </c>
-      <c r="AC20" s="7" t="s">
+      <c r="AC20" s="6" t="s">
         <v>307</v>
       </c>
     </row>
@@ -3553,28 +3571,28 @@
       <c r="U21" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V21" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="W21" s="7" t="s">
+      <c r="V21" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="W21" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X21" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y21" s="7" t="s">
+      <c r="X21" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z21" s="7" t="s">
+      <c r="Z21" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="AA21" s="7" t="s">
+      <c r="AA21" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB21" s="8">
+      <c r="AB21" s="7">
         <v>46265</v>
       </c>
-      <c r="AC21" s="7" t="s">
+      <c r="AC21" s="6" t="s">
         <v>307</v>
       </c>
     </row>
@@ -3642,28 +3660,28 @@
       <c r="U22" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V22" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="W22" s="7" t="s">
+      <c r="V22" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="W22" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X22" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y22" s="7" t="s">
+      <c r="X22" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z22" s="7" t="s">
+      <c r="Z22" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="AA22" s="7" t="s">
+      <c r="AA22" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB22" s="8">
+      <c r="AB22" s="7">
         <v>46265</v>
       </c>
-      <c r="AC22" s="7" t="s">
+      <c r="AC22" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -3731,28 +3749,28 @@
       <c r="U23" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V23" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="W23" s="7" t="s">
+      <c r="V23" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="W23" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X23" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y23" s="7" t="s">
+      <c r="X23" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z23" s="7" t="s">
+      <c r="Z23" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="AA23" s="7" t="s">
+      <c r="AA23" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB23" s="8">
+      <c r="AB23" s="7">
         <v>46265</v>
       </c>
-      <c r="AC23" s="7" t="s">
+      <c r="AC23" s="6" t="s">
         <v>309</v>
       </c>
     </row>
@@ -3820,32 +3838,32 @@
       <c r="U24" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V24" s="13" t="s">
-        <v>335</v>
-      </c>
-      <c r="W24" s="7" t="s">
+      <c r="V24" s="12" t="s">
+        <v>332</v>
+      </c>
+      <c r="W24" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X24" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y24" s="7" t="s">
+      <c r="X24" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z24" s="7" t="s">
+      <c r="Z24" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="AA24" s="7" t="s">
+      <c r="AA24" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB24" s="8">
+      <c r="AB24" s="7">
         <v>46265</v>
       </c>
-      <c r="AC24" s="7" t="s">
+      <c r="AC24" s="6" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="25" spans="1:29" ht="96" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:29" ht="128" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>114</v>
       </c>
@@ -3909,32 +3927,32 @@
       <c r="U25" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V25" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="W25" s="7" t="s">
+      <c r="V25" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="W25" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X25" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y25" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="Z25" s="7" t="s">
+      <c r="X25" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z25" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="AA25" s="7" t="s">
+      <c r="AA25" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB25" s="8">
+      <c r="AB25" s="7">
         <v>46265</v>
       </c>
-      <c r="AC25" s="7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29" ht="96" x14ac:dyDescent="0.2">
+      <c r="AC25" s="6" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" ht="112" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
         <v>114</v>
       </c>
@@ -3998,32 +4016,32 @@
       <c r="U26" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V26" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="W26" s="7" t="s">
+      <c r="V26" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="W26" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X26" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y26" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="Z26" s="7" t="s">
+      <c r="X26" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z26" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="AA26" s="7" t="s">
+      <c r="AA26" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB26" s="8">
+      <c r="AB26" s="7">
         <v>46265</v>
       </c>
-      <c r="AC26" s="7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29" ht="96" x14ac:dyDescent="0.2">
+      <c r="AC26" s="6" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" ht="128" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
         <v>114</v>
       </c>
@@ -4087,32 +4105,32 @@
       <c r="U27" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V27" s="7" t="s">
-        <v>336</v>
-      </c>
-      <c r="W27" s="7" t="s">
+      <c r="V27" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="W27" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X27" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y27" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="Z27" s="7" t="s">
+      <c r="X27" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y27" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z27" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="AA27" s="7" t="s">
+      <c r="AA27" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB27" s="8">
+      <c r="AB27" s="7">
         <v>46265</v>
       </c>
-      <c r="AC27" s="7" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29" ht="96" x14ac:dyDescent="0.2">
+      <c r="AC27" s="6" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" ht="128" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>114</v>
       </c>
@@ -4176,32 +4194,32 @@
       <c r="U28" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V28" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="W28" s="7" t="s">
+      <c r="V28" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="W28" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X28" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y28" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="Z28" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="AA28" s="7" t="s">
+      <c r="X28" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y28" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z28" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="AA28" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB28" s="8">
+      <c r="AB28" s="7">
         <v>46265</v>
       </c>
-      <c r="AC28" s="7" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="29" spans="1:29" ht="96" x14ac:dyDescent="0.2">
+      <c r="AC28" s="6" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="29" spans="1:29" ht="128" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
         <v>114</v>
       </c>
@@ -4265,29 +4283,29 @@
       <c r="U29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="V29" s="7" t="s">
-        <v>327</v>
-      </c>
-      <c r="W29" s="7" t="s">
+      <c r="V29" s="6" t="s">
+        <v>324</v>
+      </c>
+      <c r="W29" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X29" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y29" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="Z29" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="AA29" s="7" t="s">
+      <c r="X29" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y29" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z29" s="6" t="s">
+        <v>311</v>
+      </c>
+      <c r="AA29" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB29" s="8">
+      <c r="AB29" s="7">
         <v>46265</v>
       </c>
-      <c r="AC29" s="7" t="s">
-        <v>313</v>
+      <c r="AC29" s="6" t="s">
+        <v>342</v>
       </c>
     </row>
     <row r="30" spans="1:29" ht="256" x14ac:dyDescent="0.2">
@@ -4354,29 +4372,29 @@
       <c r="U30" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="V30" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="W30" s="7" t="s">
+      <c r="V30" s="12" t="s">
+        <v>334</v>
+      </c>
+      <c r="W30" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="X30" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y30" s="7" t="s">
+      <c r="X30" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y30" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z30" s="7" t="s">
-        <v>315</v>
-      </c>
-      <c r="AA30" s="7" t="s">
+      <c r="Z30" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="AA30" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB30" s="8">
+      <c r="AB30" s="7">
         <v>46265</v>
       </c>
-      <c r="AC30" s="7" t="s">
-        <v>316</v>
+      <c r="AC30" s="6" t="s">
+        <v>313</v>
       </c>
     </row>
     <row r="31" spans="1:29" ht="144" x14ac:dyDescent="0.2">
@@ -4443,29 +4461,29 @@
       <c r="U31" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="V31" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="W31" s="7" t="s">
+      <c r="V31" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="W31" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X31" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y31" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="Z31" s="7" t="s">
+      <c r="X31" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z31" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="AA31" s="7" t="s">
+      <c r="AA31" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB31" s="8">
+      <c r="AB31" s="7">
         <v>46265</v>
       </c>
-      <c r="AC31" s="7" t="s">
-        <v>314</v>
+      <c r="AC31" s="6" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="32" spans="1:29" ht="144" x14ac:dyDescent="0.2">
@@ -4532,29 +4550,29 @@
       <c r="U32" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="V32" s="7" t="s">
-        <v>332</v>
-      </c>
-      <c r="W32" s="7" t="s">
+      <c r="V32" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="W32" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X32" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y32" s="7" t="s">
-        <v>287</v>
-      </c>
-      <c r="Z32" s="7" t="s">
+      <c r="X32" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y32" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z32" s="6" t="s">
         <v>302</v>
       </c>
-      <c r="AA32" s="7" t="s">
+      <c r="AA32" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB32" s="8">
+      <c r="AB32" s="7">
         <v>46265</v>
       </c>
-      <c r="AC32" s="7" t="s">
-        <v>314</v>
+      <c r="AC32" s="6" t="s">
+        <v>343</v>
       </c>
     </row>
     <row r="33" spans="1:29" ht="96" x14ac:dyDescent="0.2">
@@ -4621,29 +4639,29 @@
       <c r="U33" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="V33" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="W33" s="7" t="s">
+      <c r="V33" s="12" t="s">
+        <v>335</v>
+      </c>
+      <c r="W33" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="X33" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y33" s="7" t="s">
+      <c r="X33" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y33" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z33" s="7" t="s">
-        <v>318</v>
-      </c>
-      <c r="AA33" s="7" t="s">
+      <c r="Z33" s="6" t="s">
+        <v>315</v>
+      </c>
+      <c r="AA33" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB33" s="8">
+      <c r="AB33" s="7">
         <v>46265</v>
       </c>
-      <c r="AC33" s="7" t="s">
-        <v>317</v>
+      <c r="AC33" s="6" t="s">
+        <v>314</v>
       </c>
     </row>
     <row r="34" spans="1:29" ht="160" x14ac:dyDescent="0.2">
@@ -4710,28 +4728,28 @@
       <c r="U34" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="V34" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="W34" s="7" t="s">
+      <c r="V34" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="W34" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X34" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y34" s="7" t="s">
+      <c r="X34" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y34" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z34" s="7" t="s">
+      <c r="Z34" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="AA34" s="7" t="s">
+      <c r="AA34" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB34" s="8">
+      <c r="AB34" s="7">
         <v>46265</v>
       </c>
-      <c r="AC34" s="7" t="s">
+      <c r="AC34" s="6" t="s">
         <v>307</v>
       </c>
     </row>
@@ -4799,28 +4817,28 @@
       <c r="U35" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="V35" s="7" t="s">
-        <v>334</v>
-      </c>
-      <c r="W35" s="7" t="s">
+      <c r="V35" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="W35" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="X35" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y35" s="7" t="s">
+      <c r="X35" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z35" s="7" t="s">
+      <c r="Z35" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="AA35" s="7" t="s">
+      <c r="AA35" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB35" s="8">
+      <c r="AB35" s="7">
         <v>46265</v>
       </c>
-      <c r="AC35" s="7" t="s">
+      <c r="AC35" s="6" t="s">
         <v>307</v>
       </c>
     </row>
@@ -4888,29 +4906,29 @@
       <c r="U36" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="V36" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="W36" s="7" t="s">
+      <c r="V36" s="12" t="s">
+        <v>336</v>
+      </c>
+      <c r="W36" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="X36" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y36" s="7" t="s">
+      <c r="X36" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y36" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z36" s="7" t="s">
+      <c r="Z36" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="AA36" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB36" s="7">
+        <v>46265</v>
+      </c>
+      <c r="AC36" s="6" t="s">
         <v>319</v>
-      </c>
-      <c r="AA36" s="7" t="s">
-        <v>288</v>
-      </c>
-      <c r="AB36" s="8">
-        <v>46265</v>
-      </c>
-      <c r="AC36" s="7" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="37" spans="1:29" ht="128" x14ac:dyDescent="0.2">
@@ -4977,29 +4995,29 @@
       <c r="U37" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="V37" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="W37" s="7" t="s">
+      <c r="V37" s="12" t="s">
+        <v>337</v>
+      </c>
+      <c r="W37" s="6" t="s">
         <v>276</v>
       </c>
-      <c r="X37" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y37" s="7" t="s">
+      <c r="X37" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y37" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="Z37" s="7" t="s">
-        <v>320</v>
-      </c>
-      <c r="AA37" s="7" t="s">
+      <c r="Z37" s="6" t="s">
+        <v>317</v>
+      </c>
+      <c r="AA37" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="AB37" s="8">
+      <c r="AB37" s="7">
         <v>46265</v>
       </c>
-      <c r="AC37" s="7" t="s">
-        <v>321</v>
+      <c r="AC37" s="6" t="s">
+        <v>318</v>
       </c>
     </row>
   </sheetData>

--- a/agent_workflows/vibe_coding/config/pairing_review_workbook.xlsx
+++ b/agent_workflows/vibe_coding/config/pairing_review_workbook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/allisonmyerspigg/GitHub/rc_sfa-rc-3-wenas-meta/agent_workflows/vibe_coding/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CD26EAE-A6BB-654D-B03A-725FFC7C636B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CDBC69-65E9-644D-B877-5EB2162960B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-15060" yWindow="-31240" windowWidth="64240" windowHeight="24460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-15340" yWindow="-20940" windowWidth="61440" windowHeight="24460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="347">
   <si>
     <t>Watershed Pairing Review</t>
   </si>
@@ -1069,6 +1069,11 @@
   <si>
     <t>There are multiple burned watersheds to a single reference site. This paper has 2 fires (High Park and Hayman Fire). B2 and B3 go to U3 (Hayman Fire). B1 go to U1 and U2 (High Park).
 I am confused about their study design too. This is also missing the Hayman fire comparisons as a line in paring worksheet here. Looking at table 1, can you pick the one reference thats closest in size to the burn here? e.g. U1 is smaller than U2, so use that to comapre to B1. For B2 and B3, they share the same reference so easier to denote the burned / unburned pair. (AMP)</t>
+  </si>
+  <si>
+    <t>This study investigates 4 burned watersheds associated with the Pole Creek Fire Complex and 6 unburned watersheds. The burn unburned pairs can get a little convuluted and we need to discuss what is best. The paper aggregated burned vs. unburned in the rest of the statistical analyses (Fig 3-8).
+from the methods : These locations included a variety of watershed sizes, burn coverages (0 to 90%), ecosystem types, and land uses (Table 1). Four sampling locations had burned areas in their watersheds, while six locations had no direct megafire influence. For one burned and one unburned watershed (sites 3 and 4 on the Spanish Fork River and sites 7 and 8 on Hobble Creek), we collected nested samples (i.e. longitudinally connected) that were upstream and downstream of major human infrastructure in the valley bottom (Fig 1 and S1 Fig). 
+This is a bit tricker since the urban/non urban influences. I think we still follow same approach, makes the methods easier to write too (ie. most downstream on the same stream) and the closest pair by size . that should give use 3 burned with unique references: 1 Benjamin Slough to 7 Hobble Creek Lower ; 2 Payson to 9 Mill Race; 3 Spanish Fork Lower to 10 Provo River.</t>
   </si>
 </sst>
 </file>
@@ -3047,7 +3052,7 @@
         <v>1</v>
       </c>
       <c r="Y15" s="6" t="s">
-        <v>284</v>
+        <v>55</v>
       </c>
       <c r="Z15" s="6" t="s">
         <v>302</v>
@@ -3062,7 +3067,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="16" spans="1:32" ht="144" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:32" ht="335" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>114</v>
       </c>
@@ -3136,7 +3141,7 @@
         <v>1</v>
       </c>
       <c r="Y16" s="6" t="s">
-        <v>284</v>
+        <v>55</v>
       </c>
       <c r="Z16" s="6" t="s">
         <v>302</v>
@@ -3148,7 +3153,7 @@
         <v>46265</v>
       </c>
       <c r="AC16" s="6" t="s">
-        <v>303</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17" spans="1:29" ht="96" x14ac:dyDescent="0.2">

--- a/agent_workflows/vibe_coding/config/pairing_review_workbook.xlsx
+++ b/agent_workflows/vibe_coding/config/pairing_review_workbook.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/allisonmyerspigg/GitHub/rc_sfa-rc-3-wenas-meta/agent_workflows/vibe_coding/config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pnnl-my.sharepoint.com/personal/jake_cavaiani_pnnl_gov/Documents/Documents/GitHub/rc_sfa-rc-3-wenas-meta/agent_workflows/vibe_coding/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CDBC69-65E9-644D-B877-5EB2162960B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{01CDBC69-65E9-644D-B877-5EB2162960B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC1CEBBC-EF56-FF4F-AE57-739EC2E24769}"/>
   <bookViews>
-    <workbookView xWindow="-15340" yWindow="-20940" windowWidth="61440" windowHeight="24460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-7640" yWindow="-28580" windowWidth="61440" windowHeight="24460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -358,9 +358,6 @@
     <t>B1</t>
   </si>
   <si>
-    <t>U1; U2</t>
-  </si>
-  <si>
     <t>Rhea et al. 2021 | Rhea_et_al_2021_C1 | Site_1 | Control_1</t>
   </si>
   <si>
@@ -670,9 +667,6 @@
     <t>Benjamin Slough</t>
   </si>
   <si>
-    <t>Hobble Creek Lower; Hobble Creek Upper</t>
-  </si>
-  <si>
     <t>Crandall et al. 2021 | Crandall_et_al_2021_C1 | Site_1 | Control_1</t>
   </si>
   <si>
@@ -685,9 +679,6 @@
     <t>Payson</t>
   </si>
   <si>
-    <t>Dry Creek; Mill Race; Mitsubishi Race</t>
-  </si>
-  <si>
     <t>Crandall et al. 2021 | Crandall_et_al_2021_C2 | Site_2 | Control_2</t>
   </si>
   <si>
@@ -932,9 +923,6 @@
   </si>
   <si>
     <t xml:space="preserve">Figure 1 in the paper shows a map of the fire perimeter with all the sampling locations. Spanish Fork Lower (burned) is compared to Provo (unburned). Spanish Fork Upper (Burned) is compared to Provo (unburned). Benjamin Slough (Burned) is compared to Hobble Creek Lower (Unburned). Payson (Burned) is compared to Misubishi, Mill Race, and Dry Creek (Unburned) </t>
-  </si>
-  <si>
-    <t>This study investigates 4 burned watersheds associated with the Pole Creek Fire Complex and 6 unburned watersheds. The burn unburned pairs can get a little convuluted and we need to discuss what is best. The paper aggregated burned vs. unburned in the rest of the statistical analyses (Fig 3-8).</t>
   </si>
   <si>
     <t xml:space="preserve">Figure 1 in the paper shows a map of the burn perimeter and the sampling locations. East Fork Kootenai and Middle Fork Kootenai are the burned watersheds associated with the Matt fire and each are compared to the West Fork Kootenai. </t>
@@ -995,9 +983,6 @@
     <t>Wragg_Fire_2015</t>
   </si>
   <si>
-    <t>Hewlett_Gulch_2012</t>
-  </si>
-  <si>
     <t>High_Park_Fire_2012</t>
   </si>
   <si>
@@ -1044,36 +1029,62 @@
   </si>
   <si>
     <t>This paper investigates 2 burned sampling locations (PSF, PNF) and compares to the same reference site (PBR). 
-Yes, relate to high park fire (AMP)</t>
-  </si>
-  <si>
-    <t>This study investigates 3 burned sites along Angora Creek that are associated with the Angora Fire. Site 1 was selected to represent the initial conditions of Angora Creek. Site 2 was within the burn area, Site 3 was located just below the burned area and site 4 was located downstream of the burn. We need to decide if they are "different" sites since they are all on the same creek. 
-Pick the most downstream site and remove the others. (AMP)</t>
-  </si>
-  <si>
-    <t>This study investigates 3 burned sites along Angora Creek that are associated with the Angora Fire. Site 1 was selected to represent the initial conditions of Angora Creek. Site 2 was within the burn area, Site 3 was located just below the burned area and site 4 was located downstream of the burn. We need to decide if they are "different" sites since they are all on the same creek. 
-Pick the most downstream site and remove the others. (AMP)</t>
-  </si>
-  <si>
-    <t>This study investigates 2 burned watersheds associated with the High Park Fire. Both burned watersheds (PNF, and PSF) compare to a single reference site (PBR). These are the same sites as from Writer et al. I think because Writer has both DOC and NO3 compared to this one that is just DOC, we should keep Writer and remove the redudancy of this paper.   
-I think this paper has higher temporal resolution than Writer? (AMP) If not, do they over lap in time? If so, then ok to drop. if not, retain (AMP)</t>
-  </si>
-  <si>
-    <t>This study investigates 4 burned watersheds associated with the Pole Creek Fire Complex and 6 unburned watersheds. The burn unburned pairs can get a little convuluted and we need to discuss what is best. The paper aggregated burned vs. unburned in the rest of the statistical analyses (Fig 3-8). Mulitple reference sites to 1 burn.
-I am OK with retaining the burned and unburned comparisions stated in the Figure 1 Evidence source. (AMP)</t>
-  </si>
-  <si>
-    <t>This study investigates 4 burned watersheds associated with the Pole Creek Fire Complex and 6 unburned watersheds. The burn unburned pairs can get a little convuluted and we need to discuss what is best. The paper aggregated burned vs. unburned in the rest of the statistical analyses (Fig 3-8). Mulitple reference sites to 1 burn.
-I am OK with retaining the burned and unburned comparisions stated in the Figure 1 Evidence source. Why is the Spanish Fork not showing up as a line on this study?? (AMP)</t>
+Yes, relate to high park fire (AMP)
+Changed from Hewlett Fire to High Park Fire 2012 (JSC - 9/15/2026).</t>
   </si>
   <si>
     <t>There are multiple burned watersheds to a single reference site. This paper has 2 fires (High Park and Hayman Fire). B2 and B3 go to U3 (Hayman Fire). B1 go to U1 and U2 (High Park).
-I am confused about their study design too. This is also missing the Hayman fire comparisons as a line in paring worksheet here. Looking at table 1, can you pick the one reference thats closest in size to the burn here? e.g. U1 is smaller than U2, so use that to comapre to B1. For B2 and B3, they share the same reference so easier to denote the burned / unburned pair. (AMP)</t>
+I am confused about their study design too. This is also missing the Hayman fire comparisons as a line in paring worksheet here. Looking at table 1, can you pick the one reference thats closest in size to the burn here? e.g. U1 is smaller than U2, so use that to comapre to B1. For B2 and B3, they share the same reference so easier to denote the burned / unburned pair. (AMP)
+B1 is 3.25 km and U1 is 7.02. So lets use U1 to compare to B1 as a 1:1 . Then B2-&gt;U3. B3-&gt;U3 (JSC 9/15/2026).</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>This study investigates 4 burned watersheds associated with the Pole Creek Fire Complex and 6 unburned watersheds. The burn unburned pairs can get a little convuluted and we need to discuss what is best. The paper aggregated burned vs. unburned in the rest of the statistical analyses (Fig 3-8).
+(3) Spanish Fork Lower (burned) compared to (10) Provo River (unburned). 1:1. JSC 9/15/2026</t>
   </si>
   <si>
     <t>This study investigates 4 burned watersheds associated with the Pole Creek Fire Complex and 6 unburned watersheds. The burn unburned pairs can get a little convuluted and we need to discuss what is best. The paper aggregated burned vs. unburned in the rest of the statistical analyses (Fig 3-8).
 from the methods : These locations included a variety of watershed sizes, burn coverages (0 to 90%), ecosystem types, and land uses (Table 1). Four sampling locations had burned areas in their watersheds, while six locations had no direct megafire influence. For one burned and one unburned watershed (sites 3 and 4 on the Spanish Fork River and sites 7 and 8 on Hobble Creek), we collected nested samples (i.e. longitudinally connected) that were upstream and downstream of major human infrastructure in the valley bottom (Fig 1 and S1 Fig). 
-This is a bit tricker since the urban/non urban influences. I think we still follow same approach, makes the methods easier to write too (ie. most downstream on the same stream) and the closest pair by size . that should give use 3 burned with unique references: 1 Benjamin Slough to 7 Hobble Creek Lower ; 2 Payson to 9 Mill Race; 3 Spanish Fork Lower to 10 Provo River.</t>
+This is a bit tricker since the urban/non urban influences. I think we still follow same approach, makes the methods easier to write too (ie. most downstream on the same stream) and the closest pair by size . that should give use 3 burned with unique references: 1 Benjamin Slough to 7 Hobble Creek Lower ; 2 Payson to 9 Mill Race; 3 Spanish Fork Lower to 10 Provo River.
+Removed from analysis as we are only comparing 3 sites as listed above (JSC 9/15/2026)</t>
+  </si>
+  <si>
+    <t>This study investigates 3 burned sites along Angora Creek that are associated with the Angora Fire. Site 1 was selected to represent the initial conditions of Angora Creek. Site 2 was within the burn area, Site 3 was located just below the burned area and site 4 was located downstream of the burn. We need to decide if they are "different" sites since they are all on the same creek. 
+Pick the most downstream site and remove the others. (AMP)
+Removed Site 2 from the analysis (JSC 9/15/2026)</t>
+  </si>
+  <si>
+    <t>This study investigates 3 burned sites along Angora Creek that are associated with the Angora Fire. Site 1 was selected to represent the initial conditions of Angora Creek. Site 2 was within the burn area, Site 3 was located just below the burned area and site 4 was located downstream of the burn. We need to decide if they are "different" sites since they are all on the same creek. 
+Pick the most downstream site and remove the others. (AMP)
+Removed Site 23from the analysis based on AMP comment. (JSC 9/15/2026)</t>
+  </si>
+  <si>
+    <t>This study investigates 3 burned sites along Angora Creek that are associated with the Angora Fire. Site 1 was selected to represent the initial conditions of Angora Creek. Site 2 was within the burn area, Site 3 was located just below the burned area and site 4 was located downstream of the burn. We need to decide if they are "different" sites since they are all on the same creek. 
+Pick the most downstream site and remove the others. (AMP)
+Site 4 (burned) compared to Site 1 (Unburned) (JSC 9/15/2026)</t>
+  </si>
+  <si>
+    <t>This study investigates 2 burned watersheds associated with the High Park Fire. Both burned watersheds (PNF, and PSF) compare to a single reference site (PBR). These are the same sites as from Writer et al. I think because Writer has both DOC and NO3 compared to this one that is just DOC, we should keep Writer and remove the redudancy of this paper.   
+I think this paper has higher temporal resolution than Writer? (AMP) If not, do they over lap in time? If so, then ok to drop. if not, retain (AMP)
+Removing this paper from the final analysis due to redundancy with Writer et al. 2014 paper (JSC 9/15/2026)</t>
+  </si>
+  <si>
+    <t>Hobble Creek Lower</t>
+  </si>
+  <si>
+    <t>This study investigates 4 burned watersheds associated with the Pole Creek Fire Complex and 6 unburned watersheds. The burn unburned pairs can get a little convuluted and we need to discuss what is best. The paper aggregated burned vs. unburned in the rest of the statistical analyses (Fig 3-8). Mulitple reference sites to 1 burn.
+I am OK with retaining the burned and unburned comparisions stated in the Figure 1 Evidence source. Why is the Spanish Fork not showing up as a line on this study?? (AMP)
+(1) Benjamin Slough (Burned) -&gt; (7) Hobble Creek Lower (Unburned). 1:1 comparison (JSC 9/15/2026)</t>
+  </si>
+  <si>
+    <t>Mill Race</t>
+  </si>
+  <si>
+    <t>This study investigates 4 burned watersheds associated with the Pole Creek Fire Complex and 6 unburned watersheds. The burn unburned pairs can get a little convuluted and we need to discuss what is best. The paper aggregated burned vs. unburned in the rest of the statistical analyses (Fig 3-8). Mulitple reference sites to 1 burn.
+I am OK with retaining the burned and unburned comparisions stated in the Figure 1 Evidence source. (AMP)
+(2) Payson (Burned) -&gt; (9) Mill Race (Unburned). 1:1 comparison (JSC 9/15/2026)</t>
   </si>
 </sst>
 </file>
@@ -1880,28 +1891,28 @@
         <v>54</v>
       </c>
       <c r="V2" s="6" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="W2" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X2" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y2" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z2" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AA2" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB2" s="7">
         <v>46265</v>
       </c>
       <c r="AC2" s="6" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="AD2" s="11"/>
       <c r="AE2"/>
@@ -1972,28 +1983,28 @@
         <v>54</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X3" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB3" s="7">
         <v>46265</v>
       </c>
       <c r="AC3" s="6" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AD3" s="11"/>
       <c r="AE3"/>
@@ -2064,28 +2075,28 @@
         <v>54</v>
       </c>
       <c r="V4" s="6" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="W4" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X4" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y4" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z4" s="6" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AA4" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB4" s="7">
         <v>46265</v>
       </c>
       <c r="AC4" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="5" spans="1:32" ht="112" x14ac:dyDescent="0.2">
@@ -2153,28 +2164,28 @@
         <v>54</v>
       </c>
       <c r="V5" s="6" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="W5" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X5" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y5" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z5" s="6" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AA5" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB5" s="7">
         <v>46265</v>
       </c>
       <c r="AC5" s="6" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="6" spans="1:32" ht="256" x14ac:dyDescent="0.2">
@@ -2242,28 +2253,28 @@
         <v>54</v>
       </c>
       <c r="V6" s="6" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="W6" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X6" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y6" s="6" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="Z6" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AA6" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB6" s="7">
         <v>46265</v>
       </c>
       <c r="AC6" s="6" t="s">
-        <v>339</v>
+        <v>334</v>
       </c>
     </row>
     <row r="7" spans="1:32" ht="256" x14ac:dyDescent="0.2">
@@ -2331,28 +2342,28 @@
         <v>54</v>
       </c>
       <c r="V7" s="6" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="W7" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X7" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y7" s="6" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="Z7" s="6" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AA7" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB7" s="7">
         <v>46265</v>
       </c>
       <c r="AC7" s="6" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="8" spans="1:32" ht="128" x14ac:dyDescent="0.2">
@@ -2420,28 +2431,28 @@
         <v>94</v>
       </c>
       <c r="V8" s="6" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="W8" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="X8" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y8" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z8" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AA8" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB8" s="7">
         <v>46265</v>
       </c>
       <c r="AC8" s="6" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" spans="1:32" ht="128" x14ac:dyDescent="0.2">
@@ -2509,28 +2520,28 @@
         <v>94</v>
       </c>
       <c r="V9" s="6" t="s">
-        <v>326</v>
+        <v>321</v>
       </c>
       <c r="W9" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="X9" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y9" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z9" s="6" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="AA9" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB9" s="7">
         <v>46265</v>
       </c>
       <c r="AC9" s="6" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" spans="1:32" ht="80" x14ac:dyDescent="0.2">
@@ -2598,31 +2609,31 @@
         <v>94</v>
       </c>
       <c r="V10" s="6" t="s">
-        <v>327</v>
+        <v>322</v>
       </c>
       <c r="W10" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="X10" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y10" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z10" s="6" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AA10" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB10" s="7">
         <v>46265</v>
       </c>
       <c r="AC10" s="6" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" ht="160" x14ac:dyDescent="0.2">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" ht="208" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>84</v>
       </c>
@@ -2642,10 +2653,10 @@
         <v>88</v>
       </c>
       <c r="G11" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>111</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>112</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>48</v>
@@ -2669,7 +2680,7 @@
         <v>1</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q11" s="1">
         <v>1</v>
@@ -2687,66 +2698,66 @@
         <v>94</v>
       </c>
       <c r="V11" s="6" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="W11" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="X11" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="6" t="s">
         <v>281</v>
       </c>
-      <c r="X11" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="6" t="s">
-        <v>55</v>
-      </c>
       <c r="Z11" s="6" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AA11" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB11" s="7">
         <v>46265</v>
       </c>
       <c r="AC11" s="6" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
     </row>
     <row r="12" spans="1:32" ht="80" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>116</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E12" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="G12" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="J12" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="K12" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M12" s="1">
         <v>2004</v>
@@ -2758,7 +2769,7 @@
         <v>2</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q12" s="1">
         <v>3</v>
@@ -2776,66 +2787,66 @@
         <v>54</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="W12" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X12" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y12" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z12" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AA12" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB12" s="7">
         <v>46265</v>
       </c>
       <c r="AC12" s="6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13" spans="1:32" ht="80" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="C13" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>127</v>
-      </c>
       <c r="I13" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J13" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="K13" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M13" s="1">
         <v>2004</v>
@@ -2847,7 +2858,7 @@
         <v>2</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q13" s="1">
         <v>3</v>
@@ -2865,66 +2876,66 @@
         <v>54</v>
       </c>
       <c r="V13" s="6" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="W13" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X13" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y13" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z13" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AA13" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB13" s="7">
         <v>46265</v>
       </c>
       <c r="AC13" s="6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="14" spans="1:32" ht="80" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B14" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="C14" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E14" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="F14" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="I14" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="J14" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="K14" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M14" s="1">
         <v>2004</v>
@@ -2936,7 +2947,7 @@
         <v>2</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q14" s="1">
         <v>3</v>
@@ -2954,60 +2965,60 @@
         <v>54</v>
       </c>
       <c r="V14" s="6" t="s">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="W14" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X14" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y14" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z14" s="6" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="AA14" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB14" s="7">
         <v>46265</v>
       </c>
       <c r="AC14" s="6" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
     </row>
     <row r="15" spans="1:32" ht="144" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B15" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>132</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E15" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F15" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="G15" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="J15" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>50</v>
@@ -3025,7 +3036,7 @@
         <v>1</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q15" s="1">
         <v>2</v>
@@ -3043,60 +3054,60 @@
         <v>54</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="W15" s="6" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="X15" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y15" s="6" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="Z15" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AA15" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB15" s="7">
         <v>46265</v>
       </c>
       <c r="AC15" s="6" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="16" spans="1:32" ht="335" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" ht="380" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="F16" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="I16" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J16" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="K16" s="1" t="s">
         <v>50</v>
@@ -3114,7 +3125,7 @@
         <v>1</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q16" s="1">
         <v>2</v>
@@ -3132,66 +3143,66 @@
         <v>54</v>
       </c>
       <c r="V16" s="6" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="W16" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X16" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="6" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="Z16" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AA16" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB16" s="7">
         <v>46265</v>
       </c>
       <c r="AC16" s="6" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:29" ht="96" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B17" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>144</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>145</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>64</v>
       </c>
       <c r="G17" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="J17" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="K17" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M17" s="1">
         <v>1985</v>
@@ -3203,7 +3214,7 @@
         <v>4</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q17" s="1">
         <v>2</v>
@@ -3221,66 +3232,66 @@
         <v>54</v>
       </c>
       <c r="V17" s="6" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="W17" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X17" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y17" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z17" s="6" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AA17" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB17" s="7">
         <v>46265</v>
       </c>
       <c r="AC17" s="6" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="18" spans="1:29" ht="96" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>64</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I18" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="J18" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="K18" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M18" s="1">
         <v>1985</v>
@@ -3292,7 +3303,7 @@
         <v>4</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="Q18" s="1">
         <v>2</v>
@@ -3310,66 +3321,66 @@
         <v>54</v>
       </c>
       <c r="V18" s="6" t="s">
-        <v>330</v>
+        <v>325</v>
       </c>
       <c r="W18" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X18" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y18" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z18" s="6" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="AA18" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB18" s="7">
         <v>46265</v>
       </c>
       <c r="AC18" s="6" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="19" spans="1:29" ht="160" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B19" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C19" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>156</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E19" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F19" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="G19" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="J19" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="K19" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M19" s="1">
         <v>1989</v>
@@ -3381,7 +3392,7 @@
         <v>4</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q19" s="1">
         <v>3</v>
@@ -3399,66 +3410,66 @@
         <v>54</v>
       </c>
       <c r="V19" s="6" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="W19" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X19" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y19" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z19" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AA19" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB19" s="7">
         <v>46265</v>
       </c>
       <c r="AC19" s="6" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20" spans="1:29" ht="160" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="E20" s="1" t="s">
+      <c r="F20" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>166</v>
-      </c>
       <c r="I20" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="K20" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M20" s="1">
         <v>1991</v>
@@ -3470,7 +3481,7 @@
         <v>2</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q20" s="1">
         <v>3</v>
@@ -3488,66 +3499,66 @@
         <v>54</v>
       </c>
       <c r="V20" s="6" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="W20" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X20" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y20" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z20" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AA20" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB20" s="7">
         <v>46265</v>
       </c>
       <c r="AC20" s="6" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" spans="1:29" ht="160" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="F21" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F21" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="I21" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J21" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M21" s="1">
         <v>1989</v>
@@ -3559,7 +3570,7 @@
         <v>3</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="Q21" s="1">
         <v>3</v>
@@ -3577,60 +3588,60 @@
         <v>54</v>
       </c>
       <c r="V21" s="6" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="W21" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X21" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y21" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z21" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AA21" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB21" s="7">
         <v>46265</v>
       </c>
       <c r="AC21" s="6" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" spans="1:29" ht="96" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B22" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>171</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>172</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F22" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="J22" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="K22" s="1" t="s">
         <v>50</v>
@@ -3648,7 +3659,7 @@
         <v>5</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q22" s="1">
         <v>3</v>
@@ -3666,60 +3677,60 @@
         <v>54</v>
       </c>
       <c r="V22" s="12" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="W22" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X22" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y22" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z22" s="6" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AA22" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB22" s="7">
         <v>46265</v>
       </c>
       <c r="AC22" s="6" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="23" spans="1:29" ht="96" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F23" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="I23" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J23" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="K23" s="1" t="s">
         <v>50</v>
@@ -3737,7 +3748,7 @@
         <v>5</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q23" s="1">
         <v>3</v>
@@ -3755,60 +3766,60 @@
         <v>54</v>
       </c>
       <c r="V23" s="12" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="W23" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X23" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y23" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z23" s="6" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AA23" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB23" s="7">
         <v>46265</v>
       </c>
       <c r="AC23" s="6" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="24" spans="1:29" ht="96" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E24" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="F24" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>184</v>
-      </c>
       <c r="I24" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="J24" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="K24" s="1" t="s">
         <v>50</v>
@@ -3826,7 +3837,7 @@
         <v>5</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="Q24" s="1">
         <v>3</v>
@@ -3844,39 +3855,39 @@
         <v>54</v>
       </c>
       <c r="V24" s="12" t="s">
-        <v>332</v>
+        <v>327</v>
       </c>
       <c r="W24" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X24" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y24" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z24" s="6" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="AA24" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB24" s="7">
         <v>46265</v>
       </c>
       <c r="AC24" s="6" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="25" spans="1:29" ht="128" x14ac:dyDescent="0.2">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="25" spans="1:29" ht="160" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="C25" s="1" t="s">
         <v>185</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>186</v>
       </c>
       <c r="D25" s="1" t="s">
         <v>62</v>
@@ -3885,25 +3896,25 @@
         <v>43</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G25" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H25" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="J25" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="K25" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M25" s="1">
         <v>2008</v>
@@ -3915,7 +3926,7 @@
         <v>2</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q25" s="1">
         <v>3</v>
@@ -3933,39 +3944,39 @@
         <v>54</v>
       </c>
       <c r="V25" s="6" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="W25" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X25" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="6" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="Z25" s="6" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AA25" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB25" s="7">
         <v>46265</v>
       </c>
       <c r="AC25" s="6" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="26" spans="1:29" ht="112" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="26" spans="1:29" ht="160" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>43</v>
@@ -3974,25 +3985,25 @@
         <v>57</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G26" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I26" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J26" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="K26" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M26" s="1">
         <v>2008</v>
@@ -4004,7 +4015,7 @@
         <v>2</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q26" s="1">
         <v>3</v>
@@ -4022,66 +4033,66 @@
         <v>54</v>
       </c>
       <c r="V26" s="6" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="W26" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X26" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="6" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="Z26" s="6" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AA26" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB26" s="7">
         <v>46265</v>
       </c>
       <c r="AC26" s="6" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="27" spans="1:29" ht="128" x14ac:dyDescent="0.2">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="27" spans="1:29" ht="160" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G27" s="1" t="s">
         <v>62</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="I27" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="J27" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="K27" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M27" s="1">
         <v>2008</v>
@@ -4093,7 +4104,7 @@
         <v>2</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="Q27" s="1">
         <v>3</v>
@@ -4111,39 +4122,39 @@
         <v>54</v>
       </c>
       <c r="V27" s="6" t="s">
-        <v>333</v>
+        <v>328</v>
       </c>
       <c r="W27" s="6" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="X27" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y27" s="6" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="Z27" s="6" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="AA27" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB27" s="7">
         <v>46265</v>
       </c>
       <c r="AC27" s="6" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="28" spans="1:29" ht="128" x14ac:dyDescent="0.2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="28" spans="1:29" ht="176" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B28" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>62</v>
@@ -4158,19 +4169,19 @@
         <v>76</v>
       </c>
       <c r="H28" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="I28" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="J28" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>199</v>
       </c>
       <c r="K28" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M28" s="1">
         <v>2013</v>
@@ -4182,7 +4193,7 @@
         <v>1</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q28" s="1">
         <v>2</v>
@@ -4200,22 +4211,22 @@
         <v>54</v>
       </c>
       <c r="V28" s="6" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="W28" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X28" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y28" s="6" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="Z28" s="6" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AA28" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB28" s="7">
         <v>46265</v>
@@ -4224,15 +4235,15 @@
         <v>342</v>
       </c>
     </row>
-    <row r="29" spans="1:29" ht="128" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:29" ht="176" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>43</v>
@@ -4247,19 +4258,19 @@
         <v>76</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="I29" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="J29" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>199</v>
       </c>
       <c r="K29" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M29" s="1">
         <v>2013</v>
@@ -4271,7 +4282,7 @@
         <v>1</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="Q29" s="1">
         <v>2</v>
@@ -4289,22 +4300,22 @@
         <v>54</v>
       </c>
       <c r="V29" s="6" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="W29" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X29" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y29" s="6" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="Z29" s="6" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="AA29" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB29" s="7">
         <v>46265</v>
@@ -4315,40 +4326,40 @@
     </row>
     <row r="30" spans="1:29" ht="256" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G30" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="J30" s="1" t="s">
         <v>210</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>211</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="M30" s="1">
         <v>2016</v>
@@ -4360,7 +4371,7 @@
         <v>1</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="Q30" s="1">
         <v>1</v>
@@ -4378,60 +4389,60 @@
         <v>94</v>
       </c>
       <c r="V30" s="12" t="s">
-        <v>334</v>
+        <v>329</v>
       </c>
       <c r="W30" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="X30" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y30" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z30" s="6" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="AA30" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB30" s="7">
         <v>46265</v>
       </c>
       <c r="AC30" s="6" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="31" spans="1:29" ht="144" x14ac:dyDescent="0.2">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="31" spans="1:29" ht="192" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>215</v>
+        <v>343</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I31" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J31" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="K31" s="1" t="s">
         <v>50</v>
@@ -4449,7 +4460,7 @@
         <v>1</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="Q31" s="1">
         <v>1</v>
@@ -4467,22 +4478,22 @@
         <v>94</v>
       </c>
       <c r="V31" s="6" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="W31" s="6" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="X31" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y31" s="6" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="Z31" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AA31" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB31" s="7">
         <v>46265</v>
@@ -4491,36 +4502,36 @@
         <v>344</v>
       </c>
     </row>
-    <row r="32" spans="1:29" ht="144" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:29" ht="192" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>97</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>220</v>
+        <v>345</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="I32" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="J32" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="K32" s="1" t="s">
         <v>50</v>
@@ -4538,7 +4549,7 @@
         <v>1</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="Q32" s="1">
         <v>1</v>
@@ -4556,66 +4567,66 @@
         <v>94</v>
       </c>
       <c r="V32" s="6" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="W32" s="6" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="X32" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y32" s="6" t="s">
-        <v>55</v>
+        <v>281</v>
       </c>
       <c r="Z32" s="6" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AA32" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB32" s="7">
         <v>46265</v>
       </c>
       <c r="AC32" s="6" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="33" spans="1:29" ht="96" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="K33" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M33" s="1">
         <v>1989</v>
@@ -4627,7 +4638,7 @@
         <v>5</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="Q33" s="1">
         <v>1</v>
@@ -4645,66 +4656,66 @@
         <v>94</v>
       </c>
       <c r="V33" s="12" t="s">
-        <v>335</v>
+        <v>330</v>
       </c>
       <c r="W33" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="X33" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y33" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z33" s="6" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="AA33" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB33" s="7">
         <v>46265</v>
       </c>
       <c r="AC33" s="6" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="34" spans="1:29" ht="160" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="I34" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J34" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="K34" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M34" s="1">
         <v>1989</v>
@@ -4716,7 +4727,7 @@
         <v>3</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="Q34" s="1">
         <v>1</v>
@@ -4734,66 +4745,66 @@
         <v>94</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X34" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y34" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AA34" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB34" s="7">
         <v>46265</v>
       </c>
       <c r="AC34" s="6" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" spans="1:29" ht="160" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D35" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>97</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="I35" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="J35" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="K35" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M35" s="1">
         <v>1989</v>
@@ -4805,7 +4816,7 @@
         <v>3</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="Q35" s="1">
         <v>1</v>
@@ -4823,66 +4834,66 @@
         <v>94</v>
       </c>
       <c r="V35" s="6" t="s">
-        <v>331</v>
+        <v>326</v>
       </c>
       <c r="W35" s="6" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="X35" s="6" t="b">
         <v>1</v>
       </c>
       <c r="Y35" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z35" s="6" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="AA35" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB35" s="7">
         <v>46265</v>
       </c>
       <c r="AC35" s="6" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
     <row r="36" spans="1:29" ht="112" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G36" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="J36" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>246</v>
       </c>
       <c r="K36" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M36" s="1">
         <v>1978</v>
@@ -4894,7 +4905,7 @@
         <v>2</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q36" s="1">
         <v>1</v>
@@ -4912,66 +4923,66 @@
         <v>94</v>
       </c>
       <c r="V36" s="12" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="W36" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="X36" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z36" s="6" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="AA36" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB36" s="7">
         <v>46265</v>
       </c>
       <c r="AC36" s="6" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" spans="1:29" ht="128" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>88</v>
       </c>
       <c r="G37" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>251</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>252</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>254</v>
       </c>
       <c r="K37" s="1" t="s">
         <v>50</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M37" s="1">
         <v>1970</v>
@@ -4983,7 +4994,7 @@
         <v>3</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="Q37" s="1">
         <v>1</v>
@@ -5001,28 +5012,28 @@
         <v>94</v>
       </c>
       <c r="V37" s="12" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="W37" s="6" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="X37" s="6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y37" s="6" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="Z37" s="6" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="AA37" s="6" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB37" s="7">
         <v>46265</v>
       </c>
       <c r="AC37" s="6" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
   </sheetData>
@@ -5071,10 +5082,10 @@
         <v>20</v>
       </c>
       <c r="D1" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E1" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F1" t="s">
         <v>29</v>
@@ -5083,10 +5094,10 @@
         <v>22</v>
       </c>
       <c r="H1" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="I1" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
@@ -5112,10 +5123,10 @@
         <v>51</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="80" x14ac:dyDescent="0.2">
@@ -5141,7 +5152,7 @@
         <v>51</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>65</v>
@@ -5170,7 +5181,7 @@
         <v>51</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>76</v>
@@ -5199,10 +5210,10 @@
         <v>51</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="16" x14ac:dyDescent="0.2">
@@ -5236,13 +5247,13 @@
     </row>
     <row r="7" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>121</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
@@ -5254,24 +5265,24 @@
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>161</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>162</v>
       </c>
       <c r="D8" s="1">
         <v>5</v>
@@ -5283,24 +5294,24 @@
         <v>0</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>176</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>177</v>
       </c>
       <c r="D9" s="1">
         <v>3</v>
@@ -5315,21 +5326,21 @@
         <v>51</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B10" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>188</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
@@ -5341,10 +5352,10 @@
         <v>0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>62</v>
@@ -5352,13 +5363,13 @@
     </row>
     <row r="11" spans="1:9" ht="32" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B11" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>137</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>138</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
@@ -5373,21 +5384,21 @@
         <v>51</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="12" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B12" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>149</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>150</v>
       </c>
       <c r="D12" s="1">
         <v>2</v>
@@ -5399,24 +5410,24 @@
         <v>0</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>199</v>
       </c>
       <c r="D13" s="1">
         <v>2</v>
@@ -5428,10 +5439,10 @@
         <v>0</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="I13" s="1" t="s">
         <v>76</v>
@@ -5439,14 +5450,14 @@
     </row>
     <row r="14" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B14" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="D14" s="1">
         <v>1</v>
       </c>
@@ -5457,100 +5468,100 @@
         <v>0</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H14" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>207</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="15" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
+      <c r="E15" s="1">
+        <v>0</v>
+      </c>
+      <c r="F15" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H15" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I15" s="1" t="s">
         <v>223</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1">
-        <v>0</v>
-      </c>
-      <c r="F15" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
+      <c r="E16" s="1">
+        <v>0</v>
+      </c>
+      <c r="F16" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="D16" s="1">
-        <v>1</v>
-      </c>
-      <c r="E16" s="1">
-        <v>0</v>
-      </c>
-      <c r="F16" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
+      <c r="E17" s="1">
+        <v>0</v>
+      </c>
+      <c r="F17" s="1" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>254</v>
-      </c>
-      <c r="D17" s="1">
-        <v>1</v>
-      </c>
-      <c r="E17" s="1">
-        <v>0</v>
-      </c>
-      <c r="F17" s="1" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -5573,10 +5584,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B1" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
@@ -5584,7 +5595,7 @@
         <v>33</v>
       </c>
       <c r="B2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -5592,7 +5603,7 @@
         <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
@@ -5600,7 +5611,7 @@
         <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -5608,7 +5619,7 @@
         <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
@@ -5616,7 +5627,7 @@
         <v>33</v>
       </c>
       <c r="B6" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
@@ -5624,7 +5635,7 @@
         <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
@@ -5632,7 +5643,7 @@
         <v>34</v>
       </c>
       <c r="B8" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
@@ -5640,7 +5651,7 @@
         <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -5656,7 +5667,7 @@
         <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.2">
@@ -5664,7 +5675,7 @@
         <v>35</v>
       </c>
       <c r="B12" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -5672,7 +5683,7 @@
         <v>35</v>
       </c>
       <c r="B13" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
@@ -5680,7 +5691,7 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
   </sheetData>

--- a/agent_workflows/vibe_coding/config/pairing_review_workbook.xlsx
+++ b/agent_workflows/vibe_coding/config/pairing_review_workbook.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pnnl-my.sharepoint.com/personal/jake_cavaiani_pnnl_gov/Documents/Documents/GitHub/rc_sfa-rc-3-wenas-meta/agent_workflows/vibe_coding/config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/allisonmyerspigg/GitHub/rc_sfa-rc-3-wenas-meta/agent_workflows/vibe_coding/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="13_ncr:1_{01CDBC69-65E9-644D-B877-5EB2162960B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC1CEBBC-EF56-FF4F-AE57-739EC2E24769}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95EDEA35-383F-474D-A15C-AA529A753551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7640" yWindow="-28580" windowWidth="61440" windowHeight="24460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-7760" yWindow="-28580" windowWidth="61440" windowHeight="24460" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -3152,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="Y16" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z16" s="6" t="s">
         <v>299</v>
@@ -3953,7 +3953,7 @@
         <v>0</v>
       </c>
       <c r="Y25" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z25" s="6" t="s">
         <v>306</v>
@@ -4042,7 +4042,7 @@
         <v>0</v>
       </c>
       <c r="Y26" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z26" s="6" t="s">
         <v>306</v>
@@ -4220,7 +4220,7 @@
         <v>0</v>
       </c>
       <c r="Y28" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z28" s="6" t="s">
         <v>307</v>
@@ -4309,7 +4309,7 @@
         <v>0</v>
       </c>
       <c r="Y29" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z29" s="6" t="s">
         <v>307</v>
@@ -4398,7 +4398,7 @@
         <v>0</v>
       </c>
       <c r="Y30" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z30" s="6" t="s">
         <v>308</v>
@@ -4932,7 +4932,7 @@
         <v>0</v>
       </c>
       <c r="Y36" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z36" s="6" t="s">
         <v>312</v>
@@ -5021,7 +5021,7 @@
         <v>0</v>
       </c>
       <c r="Y37" s="6" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="Z37" s="6" t="s">
         <v>313</v>
